--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,6 +448,24 @@
         <is>
           <t>가스켓재고</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>120</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -465,7 +465,7 @@
         <v>120</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,24 @@
       </c>
       <c r="D2" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -483,7 +483,7 @@
         <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,6 +484,24 @@
       </c>
       <c r="D3" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AR-F5103</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>120</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -501,7 +501,7 @@
         <v>120</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +502,24 @@
       </c>
       <c r="D4" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HP-F8701</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,24 @@
         <v>12</v>
       </c>
       <c r="D5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HP-F8703</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" t="n">
         <v>0</v>
       </c>
     </row>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -519,7 +519,7 @@
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -519,7 +519,7 @@
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -540,6 +540,24 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AR-F5106</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,24 +537,6 @@
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>AR-F5106</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" t="n">
         <v>0</v>
       </c>
     </row>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -540,6 +540,24 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AR-F5106 (12"x300#)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,54 +507,18 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7블럭</t>
+          <t>10블럭</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HP-F8701</t>
+          <t>AR-F5106 (12"x300#)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>7블럭</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>HP-F8703</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>7</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>AR-F5106 (12"x300#)</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" t="n">
         <v>0</v>
       </c>
     </row>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,24 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HP-F8701 (12"x300#)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" t="n">
         <v>0</v>
       </c>
     </row>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -540,6 +540,24 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HP-F8703 (12"x300#)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,6 +558,24 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TG-F7103</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -573,7 +573,7 @@
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -465,7 +465,7 @@
         <v>120</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -465,7 +465,7 @@
         <v>120</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,11 @@
           <t>가스켓재고</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>가스켓사양</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,7 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -485,6 +491,7 @@
       <c r="D3" t="n">
         <v>3</v>
       </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -501,8 +508,9 @@
         <v>120</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -521,6 +529,7 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -539,6 +548,7 @@
       <c r="D6" t="n">
         <v>0</v>
       </c>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -557,6 +567,7 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -575,6 +586,7 @@
       <c r="D8" t="n">
         <v>3</v>
       </c>
+      <c r="E8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -508,7 +508,7 @@
         <v>120</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="inlineStr"/>
     </row>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -508,7 +508,7 @@
         <v>120</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr"/>
     </row>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -508,7 +508,7 @@
         <v>120</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="inlineStr"/>
     </row>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -491,7 +491,11 @@
       <c r="D3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1042-1082-1108-1131-4.5</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -514,7 +514,11 @@
       <c r="D4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>38" x 150#</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -472,7 +472,11 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1030-1060-1104-1122-4.5</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -541,7 +541,11 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12"X300#</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -564,7 +564,11 @@
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>12"X300#</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -587,7 +587,11 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>12"X300#</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -470,7 +470,7 @@
         <v>120</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -493,7 +493,7 @@
         <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -470,7 +470,7 @@
         <v>120</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -493,7 +493,7 @@
         <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
